--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-visa_capsules_medium.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-visa_capsules_medium.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>28.74177694320679</v>
+        <v>28.91351270675659</v>
       </c>
       <c r="D2" t="n">
         <v>0.9300000071525574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1780900508165359</v>
+        <v>0.1845941692590713</v>
       </c>
       <c r="F2" t="n">
         <v>0.7734375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3569383025169372</v>
+        <v>0.1853134632110595</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07496738433837891</v>
+        <v>0.0100859994689623</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0655697211623191</v>
+        <v>0.0594222143292427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0172078092892964</v>
+        <v>0.0468316381176312</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0827148939172426</v>
+        <v>4.841279745101929</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0734493687748909</v>
+        <v>28.5226628780365</v>
       </c>
       <c r="O2" t="n">
-        <v>8.259748458862305</v>
-      </c>
-      <c r="P2" t="n">
-        <v>39.70314908027649</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>35.25569701194763</v>
+        <v>22.47918629646301</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-165848</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-161020</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>28.62914967536926</v>
+        <v>28.87967967987061</v>
       </c>
       <c r="D3" t="n">
         <v>0.9300000071525574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1779326051473617</v>
+        <v>0.1841598451137542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7811158895492554</v>
+        <v>0.7644787430763245</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7729083895683289</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3577761650085449</v>
+        <v>0.1744721829891204</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0754313990473747</v>
+        <v>0.009628086785475399</v>
       </c>
       <c r="K3" t="n">
-        <v>0.062029805034399</v>
+        <v>0.059313857058684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.015854754547278</v>
+        <v>0.0470539445678393</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0830997854471206</v>
+        <v>4.621481657028198</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0697376896937688</v>
+        <v>28.47065138816833</v>
       </c>
       <c r="O3" t="n">
-        <v>7.610282182693481</v>
-      </c>
-      <c r="P3" t="n">
-        <v>39.88789701461792</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>33.47409105300903</v>
+        <v>22.58589339256286</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-170104</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-161250</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>28.40239357948303</v>
+        <v>28.66021323204041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1742309480905532</v>
+        <v>0.1834215670824051</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7711864113807678</v>
+        <v>0.7818930149078369</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7686274647712708</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7729083895683289</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3549175858497619</v>
+        <v>0.1737268269062042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0741726756095886</v>
+        <v>0.009656387567520099</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0644623190164566</v>
+        <v>0.0583268632491429</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0160465891162554</v>
+        <v>0.0462455689907074</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0824898431698481</v>
+        <v>4.635066032409668</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0724445496996243</v>
+        <v>27.99689435958862</v>
       </c>
       <c r="O4" t="n">
-        <v>7.702362775802612</v>
-      </c>
-      <c r="P4" t="n">
-        <v>39.5951247215271</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>34.7733838558197</v>
+        <v>22.19787311553955</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-170321</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-161519</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>28.46634221076965</v>
+        <v>28.73111724853516</v>
       </c>
       <c r="D5" t="n">
         <v>0.9300000071525574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1772565692663192</v>
+        <v>0.1814704835414886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7839999794960022</v>
+        <v>0.7768595218658447</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7667984366416931</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3574284017086029</v>
+        <v>0.1659058928489685</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0754018500447273</v>
+        <v>0.0096261004606882</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0622391067445278</v>
+        <v>0.0590572064121564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0159902771313985</v>
+        <v>0.0463682542244593</v>
       </c>
       <c r="M5" t="n">
-        <v>0.084431113799413</v>
+        <v>4.620528221130371</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07033909658590951</v>
+        <v>28.34745907783508</v>
       </c>
       <c r="O5" t="n">
-        <v>7.675333023071289</v>
-      </c>
-      <c r="P5" t="n">
-        <v>40.52693462371826</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>33.76276636123657</v>
+        <v>22.25676202774048</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-170556</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-161749</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>28.34676432609558</v>
+        <v>28.54282474517822</v>
       </c>
       <c r="D6" t="n">
         <v>0.9300000071525574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1709227710962295</v>
+        <v>0.1830430626869201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7680000066757202</v>
+        <v>0.7686274647712708</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7479674816131592</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3542889952659607</v>
+        <v>0.174307644367218</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0745489746332168</v>
+        <v>0.0096741169691085</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0654758065938949</v>
+        <v>0.0586867774526278</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0158880730470021</v>
+        <v>0.0466148058573404</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0826413715879122</v>
+        <v>4.643576145172119</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07381478150685621</v>
+        <v>28.16965317726136</v>
       </c>
       <c r="O6" t="n">
-        <v>7.626275062561035</v>
-      </c>
-      <c r="P6" t="n">
-        <v>39.66785836219788</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>35.43109512329102</v>
+        <v>22.37510681152344</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-170811</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-162019</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>105.2592961788178</v>
+        <v>260.2829656600952</v>
       </c>
       <c r="D2" t="n">
-        <v>1.789999961853027</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1715812534093856</v>
+        <v>0.1959312833272493</v>
       </c>
       <c r="F2" t="n">
-        <v>0.807881772518158</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7644787430763245</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1757687628269195</v>
+        <v>0.1725579798221588</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06940938532352441</v>
+        <v>0.0094381242990493</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0631425678730011</v>
+        <v>0.0495644718408584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0102000435193379</v>
+        <v>0.0391773467262586</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0772423217693964</v>
+        <v>4.530299663543701</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0720153287053108</v>
+        <v>23.79094648361206</v>
       </c>
       <c r="O2" t="n">
-        <v>4.896020889282227</v>
-      </c>
-      <c r="P2" t="n">
-        <v>37.0763144493103</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>34.56735777854919</v>
+        <v>18.80512642860413</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250716-012359</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-173636</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>103.9952976703644</v>
+        <v>247.8511579036713</v>
       </c>
       <c r="D3" t="n">
-        <v>1.740000009536743</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1711303025484084</v>
+        <v>0.2015075696011384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8018433451652527</v>
+        <v>0.8288288116455078</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1586288958787918</v>
+        <v>0.1725797951221466</v>
       </c>
       <c r="J3" t="n">
-        <v>0.069777138531208</v>
+        <v>0.009437723457813201</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0570029206573963</v>
+        <v>0.0504349673787752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009871340294678999</v>
+        <v>0.0397161627809206</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0783321157097816</v>
+        <v>4.530107259750366</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0663329675793647</v>
+        <v>24.20878434181213</v>
       </c>
       <c r="O3" t="n">
-        <v>4.738243341445923</v>
-      </c>
-      <c r="P3" t="n">
-        <v>37.59941554069519</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>31.83982443809509</v>
+        <v>19.06375813484192</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250716-013017</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-174016</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2541649341583</v>
+        <v>352.5697758197784</v>
       </c>
       <c r="D4" t="n">
-        <v>1.820000052452088</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1722567588090896</v>
+        <v>0.1964923275841606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8416289687156677</v>
+        <v>0.8384279608726501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1547096967697143</v>
+        <v>0.1720878481864929</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0706330388784408</v>
+        <v>0.009677985310554501</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0619017258286476</v>
+        <v>0.0485470121105512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0094680463274319</v>
+        <v>0.0394795368115107</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0787298878033955</v>
+        <v>4.645432949066162</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07172283331553141</v>
+        <v>23.30256581306457</v>
       </c>
       <c r="O4" t="n">
-        <v>4.544662237167358</v>
-      </c>
-      <c r="P4" t="n">
-        <v>37.79034614562988</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>34.42695999145508</v>
+        <v>18.95017766952514</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250716-013622</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-174352</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>104.3445911407471</v>
+        <v>180.597380399704</v>
       </c>
       <c r="D5" t="n">
-        <v>1.740000009536743</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1715117663145065</v>
+        <v>0.1886861258082919</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8265306353569031</v>
+        <v>0.8309178948402405</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1463114768266677</v>
+        <v>0.1632613688707351</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0697257071733474</v>
+        <v>0.009356381992499</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0621901750564575</v>
+        <v>0.0495846554636955</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009892705579598701</v>
+        <v>0.0395210986336072</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0778402100006739</v>
+        <v>4.491063356399536</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0721856931845347</v>
+        <v>23.80063462257385</v>
       </c>
       <c r="O5" t="n">
-        <v>4.748498678207397</v>
-      </c>
-      <c r="P5" t="n">
-        <v>37.36330080032349</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>34.64913272857666</v>
+        <v>18.97012734413147</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250716-014412</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-174730</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>103.4689588546753</v>
+        <v>284.2230472564697</v>
       </c>
       <c r="D6" t="n">
-        <v>1.820000052452088</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1710077315568923</v>
+        <v>0.183287951350212</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8071748614311218</v>
+        <v>0.8247422575950623</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7692307829856873</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1737285554409027</v>
+        <v>0.1637890338897705</v>
       </c>
       <c r="J6" t="n">
-        <v>0.069757267832756</v>
+        <v>0.0095691402753194</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0623405911028385</v>
+        <v>0.0488115102052688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0103051975369453</v>
+        <v>0.0398803159594535</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0779202749331792</v>
+        <v>4.59318733215332</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0724726522962252</v>
+        <v>23.42952489852905</v>
       </c>
       <c r="O6" t="n">
-        <v>4.946494817733765</v>
-      </c>
-      <c r="P6" t="n">
-        <v>37.40173196792603</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>34.78687310218811</v>
+        <v>19.14255166053772</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250716-014910</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-175109</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>visa_capsules_medium</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5277.823351383209</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.590000152587891</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2237366958329426</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7931034564971924</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2694450914859772</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0146246934930483</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0800747712453206</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0712162618835767</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.019852876663208</v>
+      </c>
+      <c r="N2" t="n">
+        <v>38.43589019775391</v>
+      </c>
+      <c r="O2" t="n">
+        <v>34.18380570411682</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250715-040101</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>visa_capsules_medium</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5183.749615192413</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.590000152587891</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2163863576686562</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7871485948562622</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2687157988548279</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0143222590287526</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0796990181008974</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0688594634334246</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.87468433380127</v>
+      </c>
+      <c r="N3" t="n">
+        <v>38.25552868843079</v>
+      </c>
+      <c r="O3" t="n">
+        <v>33.05254244804382</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250715-053135</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>visa_capsules_medium</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5164.926976442337</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.289999961853027</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2168636456057054</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7949790954589844</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2426126599311828</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0129611576596895</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.079600744942824</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0704853902260462</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6.221355676651001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>38.20835757255554</v>
+      </c>
+      <c r="O4" t="n">
+        <v>33.8329873085022</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250715-070034</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>visa_capsules_medium</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5254.110473155975</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2197778061706217</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7876105904579163</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.23840893805027</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0135250742236773</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.07977140595515569</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.071565656363964</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.492035627365112</v>
+      </c>
+      <c r="N5" t="n">
+        <v>38.29027485847473</v>
+      </c>
+      <c r="O5" t="n">
+        <v>34.35151505470276</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250715-082912</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>visa_capsules_medium</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5228.947074890137</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.289999961853027</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2194149059117139</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.782608687877655</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2780393064022064</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0143929590781529</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0785689607262611</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0710641299684842</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.908620357513428</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37.71310114860535</v>
+      </c>
+      <c r="O6" t="n">
+        <v>34.11078238487244</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250715-095923</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_capsules_medium</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>visa_capsules_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
